--- a/Datos/IPC_Índice de Precios al Consumidor.xlsx
+++ b/Datos/IPC_Índice de Precios al Consumidor.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="3" documentId="8_{463B2510-9E9B-4172-93CB-ACACD71206A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BBD76E3-CB9D-48CF-9AA3-C5D280D5D125}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-1270" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -2712,10 +2712,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3041,12 +3037,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C864"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.08984375" customWidth="1"/>
+    <col min="1" max="2" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3054,7 +3050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3062,7 +3058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3070,7 +3066,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3078,7 +3074,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3086,7 +3082,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -3094,7 +3090,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3102,7 +3098,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3110,7 +3106,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -3118,7 +3114,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -3126,7 +3122,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -3134,7 +3130,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3142,7 +3138,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -3150,7 +3146,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3158,7 +3154,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -3166,7 +3162,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -3174,7 +3170,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -3182,7 +3178,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -3190,7 +3186,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -3198,7 +3194,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3206,7 +3202,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3214,7 +3210,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3222,7 +3218,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -3230,7 +3226,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -3238,7 +3234,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -3246,7 +3242,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -3254,7 +3250,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -3262,7 +3258,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -3270,7 +3266,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -3278,7 +3274,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -3286,7 +3282,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -3294,7 +3290,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -3302,7 +3298,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -3310,7 +3306,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -3318,7 +3314,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -3326,7 +3322,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -3334,7 +3330,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -3342,7 +3338,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -3350,7 +3346,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -3358,7 +3354,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -3366,7 +3362,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -3374,7 +3370,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -3382,7 +3378,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -3390,7 +3386,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -3398,7 +3394,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -3406,7 +3402,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -3414,7 +3410,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -3422,7 +3418,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -3430,7 +3426,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -3438,7 +3434,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -3446,7 +3442,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -3454,7 +3450,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -3462,7 +3458,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -3470,7 +3466,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -3478,7 +3474,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -3486,7 +3482,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -3494,7 +3490,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -3502,7 +3498,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -3510,7 +3506,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -3518,7 +3514,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -3526,7 +3522,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -3534,7 +3530,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -3542,7 +3538,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -3550,7 +3546,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -3558,7 +3554,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -3566,7 +3562,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -3574,7 +3570,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -3582,7 +3578,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -3590,7 +3586,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -3598,7 +3594,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -3606,7 +3602,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -3614,7 +3610,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -3622,7 +3618,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -3630,7 +3626,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -3638,7 +3634,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -3646,7 +3642,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -3654,7 +3650,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -3662,7 +3658,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -3670,7 +3666,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -3678,7 +3674,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -3686,7 +3682,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -3694,7 +3690,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -3702,7 +3698,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -3710,7 +3706,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>
@@ -3718,7 +3714,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>86</v>
       </c>
@@ -3726,7 +3722,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>87</v>
       </c>
@@ -3734,7 +3730,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>88</v>
       </c>
@@ -3742,7 +3738,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>89</v>
       </c>
@@ -3750,7 +3746,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>90</v>
       </c>
@@ -3758,7 +3754,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>91</v>
       </c>
@@ -3766,7 +3762,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -3774,7 +3770,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>93</v>
       </c>
@@ -3782,7 +3778,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>94</v>
       </c>
@@ -3790,7 +3786,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -3798,7 +3794,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -3806,7 +3802,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -3814,7 +3810,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>98</v>
       </c>
@@ -3822,7 +3818,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>99</v>
       </c>
@@ -3830,7 +3826,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>100</v>
       </c>
@@ -3838,7 +3834,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>101</v>
       </c>
@@ -3846,7 +3842,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>102</v>
       </c>
@@ -3854,7 +3850,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>103</v>
       </c>
@@ -3862,7 +3858,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>104</v>
       </c>
@@ -3870,7 +3866,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>105</v>
       </c>
@@ -3878,7 +3874,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>106</v>
       </c>
@@ -3886,7 +3882,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>107</v>
       </c>
@@ -3894,7 +3890,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>108</v>
       </c>
@@ -3902,7 +3898,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>109</v>
       </c>
@@ -3910,7 +3906,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>110</v>
       </c>
@@ -3918,7 +3914,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>111</v>
       </c>
@@ -3926,7 +3922,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>112</v>
       </c>
@@ -3934,7 +3930,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>113</v>
       </c>
@@ -3942,7 +3938,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3950,7 +3946,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3958,7 +3954,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3966,7 +3962,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3974,7 +3970,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3982,7 +3978,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>119</v>
       </c>
@@ -3990,7 +3986,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -3998,7 +3994,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>121</v>
       </c>
@@ -4006,7 +4002,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>122</v>
       </c>
@@ -4014,7 +4010,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>123</v>
       </c>
@@ -4022,7 +4018,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>124</v>
       </c>
@@ -4030,7 +4026,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>125</v>
       </c>
@@ -4038,7 +4034,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>126</v>
       </c>
@@ -4046,7 +4042,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -4054,7 +4050,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>128</v>
       </c>
@@ -4062,7 +4058,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>129</v>
       </c>
@@ -4070,7 +4066,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>130</v>
       </c>
@@ -4078,7 +4074,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>131</v>
       </c>
@@ -4086,7 +4082,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>132</v>
       </c>
@@ -4094,7 +4090,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>133</v>
       </c>
@@ -4102,7 +4098,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>134</v>
       </c>
@@ -4110,7 +4106,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>135</v>
       </c>
@@ -4118,7 +4114,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>136</v>
       </c>
@@ -4126,7 +4122,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>137</v>
       </c>
@@ -4134,7 +4130,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>138</v>
       </c>
@@ -4142,7 +4138,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>139</v>
       </c>
@@ -4150,7 +4146,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>140</v>
       </c>
@@ -4158,7 +4154,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>141</v>
       </c>
@@ -4166,7 +4162,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>142</v>
       </c>
@@ -4174,7 +4170,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>143</v>
       </c>
@@ -4182,7 +4178,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>144</v>
       </c>
@@ -4190,7 +4186,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>145</v>
       </c>
@@ -4198,7 +4194,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>146</v>
       </c>
@@ -4206,7 +4202,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>147</v>
       </c>
@@ -4214,7 +4210,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>148</v>
       </c>
@@ -4222,7 +4218,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>149</v>
       </c>
@@ -4230,7 +4226,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>150</v>
       </c>
@@ -4238,7 +4234,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>151</v>
       </c>
@@ -4246,7 +4242,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>152</v>
       </c>
@@ -4254,7 +4250,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>153</v>
       </c>
@@ -4262,7 +4258,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>154</v>
       </c>
@@ -4270,7 +4266,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>155</v>
       </c>
@@ -4278,7 +4274,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>156</v>
       </c>
@@ -4286,7 +4282,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>157</v>
       </c>
@@ -4294,7 +4290,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>158</v>
       </c>
@@ -4302,7 +4298,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>159</v>
       </c>
@@ -4310,7 +4306,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>160</v>
       </c>
@@ -4318,7 +4314,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>161</v>
       </c>
@@ -4326,7 +4322,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>162</v>
       </c>
@@ -4334,7 +4330,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>163</v>
       </c>
@@ -4342,7 +4338,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>164</v>
       </c>
@@ -4350,7 +4346,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>165</v>
       </c>
@@ -4358,7 +4354,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>166</v>
       </c>
@@ -4366,7 +4362,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>167</v>
       </c>
@@ -4374,7 +4370,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>168</v>
       </c>
@@ -4382,7 +4378,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>169</v>
       </c>
@@ -4390,7 +4386,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>170</v>
       </c>
@@ -4398,7 +4394,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>171</v>
       </c>
@@ -4406,7 +4402,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>172</v>
       </c>
@@ -4414,7 +4410,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>173</v>
       </c>
@@ -4422,7 +4418,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>174</v>
       </c>
@@ -4430,7 +4426,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>175</v>
       </c>
@@ -4438,7 +4434,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>176</v>
       </c>
@@ -4446,7 +4442,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>177</v>
       </c>
@@ -4454,7 +4450,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>178</v>
       </c>
@@ -4462,7 +4458,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>179</v>
       </c>
@@ -4470,7 +4466,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>180</v>
       </c>
@@ -4478,7 +4474,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>181</v>
       </c>
@@ -4486,7 +4482,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>182</v>
       </c>
@@ -4494,7 +4490,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>183</v>
       </c>
@@ -4502,7 +4498,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>184</v>
       </c>
@@ -4510,7 +4506,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>185</v>
       </c>
@@ -4518,7 +4514,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>186</v>
       </c>
@@ -4526,7 +4522,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>187</v>
       </c>
@@ -4534,7 +4530,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>188</v>
       </c>
@@ -4542,7 +4538,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>189</v>
       </c>
@@ -4550,7 +4546,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>190</v>
       </c>
@@ -4558,7 +4554,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>191</v>
       </c>
@@ -4566,7 +4562,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>192</v>
       </c>
@@ -4574,7 +4570,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>193</v>
       </c>
@@ -4582,7 +4578,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>194</v>
       </c>
@@ -4590,7 +4586,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>195</v>
       </c>
@@ -4598,7 +4594,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>196</v>
       </c>
@@ -4606,7 +4602,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>197</v>
       </c>
@@ -4614,7 +4610,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>198</v>
       </c>
@@ -4622,7 +4618,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>199</v>
       </c>
@@ -4630,7 +4626,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>200</v>
       </c>
@@ -4638,7 +4634,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>201</v>
       </c>
@@ -4646,7 +4642,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>202</v>
       </c>
@@ -4654,7 +4650,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>203</v>
       </c>
@@ -4662,7 +4658,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>204</v>
       </c>
@@ -4670,7 +4666,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>205</v>
       </c>
@@ -4678,7 +4674,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>206</v>
       </c>
@@ -4686,7 +4682,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>207</v>
       </c>
@@ -4694,7 +4690,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>208</v>
       </c>
@@ -4702,7 +4698,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>209</v>
       </c>
@@ -4710,7 +4706,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>210</v>
       </c>
@@ -4718,7 +4714,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>211</v>
       </c>
@@ -4726,7 +4722,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>212</v>
       </c>
@@ -4734,7 +4730,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>213</v>
       </c>
@@ -4742,7 +4738,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>214</v>
       </c>
@@ -4750,7 +4746,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>215</v>
       </c>
@@ -4758,7 +4754,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>216</v>
       </c>
@@ -4766,7 +4762,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>217</v>
       </c>
@@ -4774,7 +4770,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>218</v>
       </c>
@@ -4782,7 +4778,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>219</v>
       </c>
@@ -4790,7 +4786,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>220</v>
       </c>
@@ -4798,7 +4794,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>221</v>
       </c>
@@ -4806,7 +4802,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>222</v>
       </c>
@@ -4814,7 +4810,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>223</v>
       </c>
@@ -4822,7 +4818,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>224</v>
       </c>
@@ -4830,7 +4826,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>225</v>
       </c>
@@ -4838,7 +4834,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>226</v>
       </c>
@@ -4846,7 +4842,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>227</v>
       </c>
@@ -4854,7 +4850,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>228</v>
       </c>
@@ -4862,7 +4858,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>229</v>
       </c>
@@ -4870,7 +4866,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>230</v>
       </c>
@@ -4878,7 +4874,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>231</v>
       </c>
@@ -4886,7 +4882,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>232</v>
       </c>
@@ -4894,7 +4890,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>233</v>
       </c>
@@ -4902,7 +4898,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>234</v>
       </c>
@@ -4910,7 +4906,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>235</v>
       </c>
@@ -4918,7 +4914,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>236</v>
       </c>
@@ -4926,7 +4922,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>237</v>
       </c>
@@ -4934,7 +4930,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>238</v>
       </c>
@@ -4942,7 +4938,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>239</v>
       </c>
@@ -4950,7 +4946,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>240</v>
       </c>
@@ -4958,7 +4954,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>241</v>
       </c>
@@ -4966,7 +4962,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>242</v>
       </c>
@@ -4974,7 +4970,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>243</v>
       </c>
@@ -4982,7 +4978,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>244</v>
       </c>
@@ -4990,7 +4986,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>245</v>
       </c>
@@ -4998,7 +4994,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>246</v>
       </c>
@@ -5006,7 +5002,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>247</v>
       </c>
@@ -5014,7 +5010,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>248</v>
       </c>
@@ -5022,7 +5018,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>249</v>
       </c>
@@ -5030,7 +5026,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>250</v>
       </c>
@@ -5038,7 +5034,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>251</v>
       </c>
@@ -5046,7 +5042,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>252</v>
       </c>
@@ -5054,7 +5050,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>253</v>
       </c>
@@ -5062,7 +5058,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>254</v>
       </c>
@@ -5070,7 +5066,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>255</v>
       </c>
@@ -5078,7 +5074,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>256</v>
       </c>
@@ -5086,7 +5082,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>257</v>
       </c>
@@ -5094,7 +5090,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>258</v>
       </c>
@@ -5102,7 +5098,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>259</v>
       </c>
@@ -5110,7 +5106,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>260</v>
       </c>
@@ -5118,7 +5114,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>261</v>
       </c>
@@ -5126,7 +5122,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>262</v>
       </c>
@@ -5134,7 +5130,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>263</v>
       </c>
@@ -5142,7 +5138,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>264</v>
       </c>
@@ -5150,7 +5146,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>265</v>
       </c>
@@ -5158,7 +5154,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>266</v>
       </c>
@@ -5166,7 +5162,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>267</v>
       </c>
@@ -5174,7 +5170,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>268</v>
       </c>
@@ -5182,7 +5178,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>269</v>
       </c>
@@ -5190,7 +5186,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>270</v>
       </c>
@@ -5198,7 +5194,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>271</v>
       </c>
@@ -5206,7 +5202,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>272</v>
       </c>
@@ -5214,7 +5210,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>273</v>
       </c>
@@ -5222,7 +5218,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>274</v>
       </c>
@@ -5230,7 +5226,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>275</v>
       </c>
@@ -5238,7 +5234,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>276</v>
       </c>
@@ -5246,7 +5242,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>277</v>
       </c>
@@ -5254,7 +5250,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>278</v>
       </c>
@@ -5262,7 +5258,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>279</v>
       </c>
@@ -5270,7 +5266,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>280</v>
       </c>
@@ -5278,7 +5274,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>281</v>
       </c>
@@ -5286,7 +5282,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>282</v>
       </c>
@@ -5294,7 +5290,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>283</v>
       </c>
@@ -5302,7 +5298,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>284</v>
       </c>
@@ -5310,7 +5306,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>285</v>
       </c>
@@ -5318,7 +5314,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>286</v>
       </c>
@@ -5326,7 +5322,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>287</v>
       </c>
@@ -5334,7 +5330,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>288</v>
       </c>
@@ -5342,7 +5338,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>289</v>
       </c>
@@ -5350,7 +5346,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>290</v>
       </c>
@@ -5358,7 +5354,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>291</v>
       </c>
@@ -5366,7 +5362,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>292</v>
       </c>
@@ -5374,7 +5370,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>293</v>
       </c>
@@ -5382,7 +5378,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>294</v>
       </c>
@@ -5390,7 +5386,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>295</v>
       </c>
@@ -5398,7 +5394,7 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>296</v>
       </c>
@@ -5406,7 +5402,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>297</v>
       </c>
@@ -5414,7 +5410,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>298</v>
       </c>
@@ -5422,7 +5418,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>299</v>
       </c>
@@ -5430,7 +5426,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>300</v>
       </c>
@@ -5438,7 +5434,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>301</v>
       </c>
@@ -5446,7 +5442,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>302</v>
       </c>
@@ -5454,7 +5450,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>303</v>
       </c>
@@ -5462,7 +5458,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>304</v>
       </c>
@@ -5470,7 +5466,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>305</v>
       </c>
@@ -5478,7 +5474,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>306</v>
       </c>
@@ -5486,7 +5482,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>307</v>
       </c>
@@ -5494,7 +5490,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>308</v>
       </c>
@@ -5502,7 +5498,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>309</v>
       </c>
@@ -5510,7 +5506,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>310</v>
       </c>
@@ -5518,7 +5514,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>311</v>
       </c>
@@ -5526,7 +5522,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>312</v>
       </c>
@@ -5534,7 +5530,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>313</v>
       </c>
@@ -5542,7 +5538,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>314</v>
       </c>
@@ -5550,7 +5546,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>315</v>
       </c>
@@ -5558,7 +5554,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>316</v>
       </c>
@@ -5566,7 +5562,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>317</v>
       </c>
@@ -5574,7 +5570,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>318</v>
       </c>
@@ -5582,7 +5578,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>319</v>
       </c>
@@ -5590,7 +5586,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>320</v>
       </c>
@@ -5598,7 +5594,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>321</v>
       </c>
@@ -5606,7 +5602,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>322</v>
       </c>
@@ -5614,7 +5610,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>323</v>
       </c>
@@ -5622,7 +5618,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>324</v>
       </c>
@@ -5630,7 +5626,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>325</v>
       </c>
@@ -5638,7 +5634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>326</v>
       </c>
@@ -5646,7 +5642,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>327</v>
       </c>
@@ -5654,7 +5650,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>328</v>
       </c>
@@ -5662,7 +5658,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>329</v>
       </c>
@@ -5670,7 +5666,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>330</v>
       </c>
@@ -5678,7 +5674,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>331</v>
       </c>
@@ -5686,7 +5682,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>332</v>
       </c>
@@ -5694,7 +5690,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>333</v>
       </c>
@@ -5702,7 +5698,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>334</v>
       </c>
@@ -5710,7 +5706,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>335</v>
       </c>
@@ -5718,7 +5714,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>336</v>
       </c>
@@ -5726,7 +5722,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>337</v>
       </c>
@@ -5734,7 +5730,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>338</v>
       </c>
@@ -5742,7 +5738,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>339</v>
       </c>
@@ -5750,7 +5746,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>340</v>
       </c>
@@ -5758,7 +5754,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>341</v>
       </c>
@@ -5766,7 +5762,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>342</v>
       </c>
@@ -5774,7 +5770,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>343</v>
       </c>
@@ -5782,7 +5778,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>344</v>
       </c>
@@ -5790,7 +5786,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>345</v>
       </c>
@@ -5798,7 +5794,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>346</v>
       </c>
@@ -5806,7 +5802,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>347</v>
       </c>
@@ -5814,7 +5810,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>348</v>
       </c>
@@ -5822,7 +5818,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>349</v>
       </c>
@@ -5830,7 +5826,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>350</v>
       </c>
@@ -5838,7 +5834,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>351</v>
       </c>
@@ -5846,7 +5842,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>352</v>
       </c>
@@ -5854,7 +5850,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>353</v>
       </c>
@@ -5862,7 +5858,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>354</v>
       </c>
@@ -5870,7 +5866,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>355</v>
       </c>
@@ -5878,7 +5874,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>356</v>
       </c>
@@ -5886,7 +5882,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>357</v>
       </c>
@@ -5894,7 +5890,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>358</v>
       </c>
@@ -5902,7 +5898,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>359</v>
       </c>
@@ -5910,7 +5906,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>360</v>
       </c>
@@ -5918,7 +5914,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>361</v>
       </c>
@@ -5926,7 +5922,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>362</v>
       </c>
@@ -5934,7 +5930,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>363</v>
       </c>
@@ -5942,7 +5938,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>364</v>
       </c>
@@ -5950,7 +5946,7 @@
         <v>1.83</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>365</v>
       </c>
@@ -5958,7 +5954,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>366</v>
       </c>
@@ -5966,7 +5962,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>367</v>
       </c>
@@ -5974,7 +5970,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>368</v>
       </c>
@@ -5982,7 +5978,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>369</v>
       </c>
@@ -5990,7 +5986,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>370</v>
       </c>
@@ -5998,7 +5994,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>371</v>
       </c>
@@ -6006,7 +6002,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>372</v>
       </c>
@@ -6014,7 +6010,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>373</v>
       </c>
@@ -6022,7 +6018,7 @@
         <v>2.17</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>374</v>
       </c>
@@ -6030,7 +6026,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>375</v>
       </c>
@@ -6038,7 +6034,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>376</v>
       </c>
@@ -6046,7 +6042,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>377</v>
       </c>
@@ -6054,7 +6050,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>378</v>
       </c>
@@ -6062,7 +6058,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>379</v>
       </c>
@@ -6070,7 +6066,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>380</v>
       </c>
@@ -6078,7 +6074,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>381</v>
       </c>
@@ -6086,7 +6082,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>382</v>
       </c>
@@ -6094,7 +6090,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>383</v>
       </c>
@@ -6102,7 +6098,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>384</v>
       </c>
@@ -6110,7 +6106,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>385</v>
       </c>
@@ -6118,7 +6114,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>386</v>
       </c>
@@ -6126,7 +6122,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>387</v>
       </c>
@@ -6134,7 +6130,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>388</v>
       </c>
@@ -6142,7 +6138,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>389</v>
       </c>
@@ -6150,7 +6146,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>390</v>
       </c>
@@ -6158,7 +6154,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>391</v>
       </c>
@@ -6166,7 +6162,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>392</v>
       </c>
@@ -6174,7 +6170,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>393</v>
       </c>
@@ -6182,7 +6178,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>394</v>
       </c>
@@ -6190,7 +6186,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>395</v>
       </c>
@@ -6198,7 +6194,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>396</v>
       </c>
@@ -6206,7 +6202,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>397</v>
       </c>
@@ -6214,7 +6210,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>398</v>
       </c>
@@ -6222,7 +6218,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>399</v>
       </c>
@@ -6230,7 +6226,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>400</v>
       </c>
@@ -6238,7 +6234,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>401</v>
       </c>
@@ -6246,7 +6242,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>402</v>
       </c>
@@ -6254,7 +6250,7 @@
         <v>3.37</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>403</v>
       </c>
@@ -6262,7 +6258,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>404</v>
       </c>
@@ -6270,7 +6266,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>405</v>
       </c>
@@ -6278,7 +6274,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>406</v>
       </c>
@@ -6286,7 +6282,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>407</v>
       </c>
@@ -6294,7 +6290,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>408</v>
       </c>
@@ -6302,7 +6298,7 @@
         <v>3.94</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>409</v>
       </c>
@@ -6310,7 +6306,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>410</v>
       </c>
@@ -6318,7 +6314,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>411</v>
       </c>
@@ -6326,7 +6322,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>412</v>
       </c>
@@ -6334,7 +6330,7 @@
         <v>4.33</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>413</v>
       </c>
@@ -6342,7 +6338,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>414</v>
       </c>
@@ -6350,7 +6346,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>415</v>
       </c>
@@ -6358,7 +6354,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>416</v>
       </c>
@@ -6366,7 +6362,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>417</v>
       </c>
@@ -6374,7 +6370,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>418</v>
       </c>
@@ -6382,7 +6378,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>419</v>
       </c>
@@ -6390,7 +6386,7 @@
         <v>4.87</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>420</v>
       </c>
@@ -6398,7 +6394,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>421</v>
       </c>
@@ -6406,7 +6402,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>422</v>
       </c>
@@ -6414,7 +6410,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>423</v>
       </c>
@@ -6422,7 +6418,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>424</v>
       </c>
@@ -6430,7 +6426,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>425</v>
       </c>
@@ -6438,7 +6434,7 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>426</v>
       </c>
@@ -6446,7 +6442,7 @@
         <v>5.51</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>427</v>
       </c>
@@ -6454,7 +6450,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>428</v>
       </c>
@@ -6462,7 +6458,7 @@
         <v>5.7</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>429</v>
       </c>
@@ -6470,7 +6466,7 @@
         <v>5.78</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>430</v>
       </c>
@@ -6478,7 +6474,7 @@
         <v>5.97</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>431</v>
       </c>
@@ -6486,7 +6482,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>432</v>
       </c>
@@ -6494,7 +6490,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>433</v>
       </c>
@@ -6502,7 +6498,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>434</v>
       </c>
@@ -6510,7 +6506,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>435</v>
       </c>
@@ -6518,7 +6514,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>436</v>
       </c>
@@ -6526,7 +6522,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>437</v>
       </c>
@@ -6534,7 +6530,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>438</v>
       </c>
@@ -6542,7 +6538,7 @@
         <v>7.18</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>439</v>
       </c>
@@ -6550,7 +6546,7 @@
         <v>7.31</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>440</v>
       </c>
@@ -6558,7 +6554,7 @@
         <v>7.46</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>441</v>
       </c>
@@ -6566,7 +6562,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>442</v>
       </c>
@@ -6574,7 +6570,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>443</v>
       </c>
@@ -6582,7 +6578,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>444</v>
       </c>
@@ -6590,7 +6586,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>445</v>
       </c>
@@ -6598,7 +6594,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>446</v>
       </c>
@@ -6606,7 +6602,7 @@
         <v>8.7799999999999994</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>447</v>
       </c>
@@ -6614,7 +6610,7 @@
         <v>8.92</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>448</v>
       </c>
@@ -6622,7 +6618,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>449</v>
       </c>
@@ -6630,7 +6626,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>450</v>
       </c>
@@ -6638,7 +6634,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>451</v>
       </c>
@@ -6646,7 +6642,7 @@
         <v>9.4499999999999993</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>452</v>
       </c>
@@ -6654,7 +6650,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>453</v>
       </c>
@@ -6662,7 +6658,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>454</v>
       </c>
@@ -6670,7 +6666,7 @@
         <v>10.039999999999999</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>455</v>
       </c>
@@ -6678,7 +6674,7 @@
         <v>10.38</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>456</v>
       </c>
@@ -6686,7 +6682,7 @@
         <v>10.62</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>457</v>
       </c>
@@ -6694,7 +6690,7 @@
         <v>10.92</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>458</v>
       </c>
@@ -6702,7 +6698,7 @@
         <v>11.18</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>459</v>
       </c>
@@ -6710,7 +6706,7 @@
         <v>11.43</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>460</v>
       </c>
@@ -6718,7 +6714,7 @@
         <v>11.66</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>461</v>
       </c>
@@ -6726,7 +6722,7 @@
         <v>11.74</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>462</v>
       </c>
@@ -6734,7 +6730,7 @@
         <v>11.84</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>463</v>
       </c>
@@ -6742,7 +6738,7 @@
         <v>11.94</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>464</v>
       </c>
@@ -6750,7 +6746,7 @@
         <v>12.03</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>465</v>
       </c>
@@ -6758,7 +6754,7 @@
         <v>12.14</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>466</v>
       </c>
@@ -6766,7 +6762,7 @@
         <v>12.54</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>467</v>
       </c>
@@ -6774,7 +6770,7 @@
         <v>12.94</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>468</v>
       </c>
@@ -6782,7 +6778,7 @@
         <v>13.19</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>469</v>
       </c>
@@ -6790,7 +6786,7 @@
         <v>13.44</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>470</v>
       </c>
@@ -6798,7 +6794,7 @@
         <v>13.66</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>471</v>
       </c>
@@ -6806,7 +6802,7 @@
         <v>13.87</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>472</v>
       </c>
@@ -6814,7 +6810,7 @@
         <v>14.04</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>473</v>
       </c>
@@ -6822,7 +6818,7 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>474</v>
       </c>
@@ -6830,7 +6826,7 @@
         <v>14.38</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>475</v>
       </c>
@@ -6838,7 +6834,7 @@
         <v>14.53</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>476</v>
       </c>
@@ -6846,7 +6842,7 @@
         <v>14.72</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>477</v>
       </c>
@@ -6854,7 +6850,7 @@
         <v>14.89</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>478</v>
       </c>
@@ -6862,7 +6858,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>479</v>
       </c>
@@ -6870,7 +6866,7 @@
         <v>15.92</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>480</v>
       </c>
@@ -6878,7 +6874,7 @@
         <v>16.27</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>481</v>
       </c>
@@ -6886,7 +6882,7 @@
         <v>16.66</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>482</v>
       </c>
@@ -6894,7 +6890,7 @@
         <v>16.920000000000002</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>483</v>
       </c>
@@ -6902,7 +6898,7 @@
         <v>17.07</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>484</v>
       </c>
@@ -6910,7 +6906,7 @@
         <v>17.23</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>485</v>
       </c>
@@ -6918,7 +6914,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>486</v>
       </c>
@@ -6926,7 +6922,7 @@
         <v>17.59</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>487</v>
       </c>
@@ -6934,7 +6930,7 @@
         <v>17.78</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>488</v>
       </c>
@@ -6942,7 +6938,7 @@
         <v>17.98</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>489</v>
       </c>
@@ -6950,7 +6946,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>490</v>
       </c>
@@ -6958,7 +6954,7 @@
         <v>18.59</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>491</v>
       </c>
@@ -6966,7 +6962,7 @@
         <v>19.239999999999998</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>492</v>
       </c>
@@ -6974,7 +6970,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>493</v>
       </c>
@@ -6982,7 +6978,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>494</v>
       </c>
@@ -6990,7 +6986,7 @@
         <v>20.52</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>495</v>
       </c>
@@ -6998,7 +6994,7 @@
         <v>20.77</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>496</v>
       </c>
@@ -7006,7 +7002,7 @@
         <v>20.93</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>497</v>
       </c>
@@ -7014,7 +7010,7 @@
         <v>21.07</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>498</v>
       </c>
@@ -7022,7 +7018,7 @@
         <v>21.24</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>499</v>
       </c>
@@ -7030,7 +7026,7 @@
         <v>21.43</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>500</v>
       </c>
@@ -7038,7 +7034,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>501</v>
       </c>
@@ -7046,7 +7042,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>502</v>
       </c>
@@ -7054,7 +7050,7 @@
         <v>22.35</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>503</v>
       </c>
@@ -7062,7 +7058,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>504</v>
       </c>
@@ -7070,7 +7066,7 @@
         <v>23.74</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>505</v>
       </c>
@@ -7078,7 +7074,7 @@
         <v>24.21</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>506</v>
       </c>
@@ -7086,7 +7082,7 @@
         <v>24.58</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>507</v>
       </c>
@@ -7094,7 +7090,7 @@
         <v>24.87</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>508</v>
       </c>
@@ -7102,7 +7098,7 @@
         <v>25.24</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>509</v>
       </c>
@@ -7110,7 +7106,7 @@
         <v>25.52</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>510</v>
       </c>
@@ -7118,7 +7114,7 @@
         <v>25.82</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>511</v>
       </c>
@@ -7126,7 +7122,7 @@
         <v>26.12</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>512</v>
       </c>
@@ -7134,7 +7130,7 @@
         <v>26.33</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>513</v>
       </c>
@@ -7142,7 +7138,7 @@
         <v>26.52</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>514</v>
       </c>
@@ -7150,7 +7146,7 @@
         <v>26.96</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>515</v>
       </c>
@@ -7158,7 +7154,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>516</v>
       </c>
@@ -7166,7 +7162,7 @@
         <v>28.23</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>517</v>
       </c>
@@ -7174,7 +7170,7 @@
         <v>28.69</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>518</v>
       </c>
@@ -7182,7 +7178,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>519</v>
       </c>
@@ -7190,7 +7186,7 @@
         <v>29.51</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>520</v>
       </c>
@@ -7198,7 +7194,7 @@
         <v>29.76</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>521</v>
       </c>
@@ -7206,7 +7202,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>522</v>
       </c>
@@ -7214,7 +7210,7 @@
         <v>30.48</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>523</v>
       </c>
@@ -7222,7 +7218,7 @@
         <v>30.77</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>524</v>
       </c>
@@ -7230,7 +7226,7 @@
         <v>31.02</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>525</v>
       </c>
@@ -7238,7 +7234,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>526</v>
       </c>
@@ -7246,7 +7242,7 @@
         <v>31.77</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>527</v>
       </c>
@@ -7254,7 +7250,7 @@
         <v>32.81</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>528</v>
       </c>
@@ -7262,7 +7258,7 @@
         <v>33.67</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>529</v>
       </c>
@@ -7270,7 +7266,7 @@
         <v>34.65</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>530</v>
       </c>
@@ -7278,7 +7274,7 @@
         <v>35.19</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>531</v>
       </c>
@@ -7286,7 +7282,7 @@
         <v>35.619999999999997</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>532</v>
       </c>
@@ -7294,7 +7290,7 @@
         <v>35.79</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>533</v>
       </c>
@@ -7302,7 +7298,7 @@
         <v>35.799999999999997</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>534</v>
       </c>
@@ -7310,7 +7306,7 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>535</v>
       </c>
@@ -7318,7 +7314,7 @@
         <v>36.03</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>536</v>
       </c>
@@ -7326,7 +7322,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>537</v>
       </c>
@@ -7334,7 +7330,7 @@
         <v>36.42</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>538</v>
       </c>
@@ -7342,7 +7338,7 @@
         <v>37.229999999999997</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>539</v>
       </c>
@@ -7350,7 +7346,7 @@
         <v>37.86</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>540</v>
       </c>
@@ -7358,7 +7354,7 @@
         <v>38.22</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>541</v>
       </c>
@@ -7366,7 +7362,7 @@
         <v>38.520000000000003</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>542</v>
       </c>
@@ -7374,7 +7370,7 @@
         <v>38.700000000000003</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>543</v>
       </c>
@@ -7382,7 +7378,7 @@
         <v>38.81</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>544</v>
       </c>
@@ -7390,7 +7386,7 @@
         <v>38.93</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>545</v>
       </c>
@@ -7398,7 +7394,7 @@
         <v>39.119999999999997</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>546</v>
       </c>
@@ -7406,7 +7402,7 @@
         <v>39.25</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>547</v>
       </c>
@@ -7414,7 +7410,7 @@
         <v>39.39</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>548</v>
       </c>
@@ -7422,7 +7418,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>549</v>
       </c>
@@ -7430,7 +7426,7 @@
         <v>39.79</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>550</v>
       </c>
@@ -7438,7 +7434,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>551</v>
       </c>
@@ -7446,7 +7442,7 @@
         <v>41.23</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>552</v>
       </c>
@@ -7454,7 +7450,7 @@
         <v>41.93</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>553</v>
       </c>
@@ -7462,7 +7458,7 @@
         <v>42.35</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>554</v>
       </c>
@@ -7470,7 +7466,7 @@
         <v>42.57</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>555</v>
       </c>
@@ -7478,7 +7474,7 @@
         <v>42.56</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>556</v>
       </c>
@@ -7486,7 +7482,7 @@
         <v>42.55</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>557</v>
       </c>
@@ -7494,7 +7490,7 @@
         <v>42.68</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>558</v>
       </c>
@@ -7502,7 +7498,7 @@
         <v>42.86</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>559</v>
       </c>
@@ -7510,7 +7506,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>560</v>
       </c>
@@ -7518,7 +7514,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>561</v>
       </c>
@@ -7526,7 +7522,7 @@
         <v>43.27</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>562</v>
       </c>
@@ -7534,7 +7530,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>563</v>
       </c>
@@ -7542,7 +7538,7 @@
         <v>44.55</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>564</v>
       </c>
@@ -7550,7 +7546,7 @@
         <v>45.21</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>565</v>
       </c>
@@ -7558,7 +7554,7 @@
         <v>45.73</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>566</v>
       </c>
@@ -7566,7 +7562,7 @@
         <v>45.92</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>567</v>
       </c>
@@ -7574,7 +7570,7 @@
         <v>45.94</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>568</v>
       </c>
@@ -7582,7 +7578,7 @@
         <v>45.99</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>569</v>
       </c>
@@ -7590,7 +7586,7 @@
         <v>46.11</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>570</v>
       </c>
@@ -7598,7 +7594,7 @@
         <v>46.28</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>571</v>
       </c>
@@ -7606,7 +7602,7 @@
         <v>46.37</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>572</v>
       </c>
@@ -7614,7 +7610,7 @@
         <v>46.42</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>573</v>
       </c>
@@ -7622,7 +7618,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>574</v>
       </c>
@@ -7630,7 +7626,7 @@
         <v>46.95</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>575</v>
       </c>
@@ -7638,7 +7634,7 @@
         <v>47.54</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>576</v>
       </c>
@@ -7646,7 +7642,7 @@
         <v>47.87</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>577</v>
       </c>
@@ -7654,7 +7650,7 @@
         <v>48.31</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>578</v>
       </c>
@@ -7662,7 +7658,7 @@
         <v>48.6</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>579</v>
       </c>
@@ -7670,7 +7666,7 @@
         <v>48.81</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>580</v>
       </c>
@@ -7678,7 +7674,7 @@
         <v>48.82</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>581</v>
       </c>
@@ -7686,7 +7682,7 @@
         <v>48.87</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>582</v>
       </c>
@@ -7694,7 +7690,7 @@
         <v>49.04</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>583</v>
       </c>
@@ -7702,7 +7698,7 @@
         <v>49.32</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>584</v>
       </c>
@@ -7710,7 +7706,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>585</v>
       </c>
@@ -7718,7 +7714,7 @@
         <v>49.83</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>586</v>
       </c>
@@ -7726,7 +7722,7 @@
         <v>50.42</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>587</v>
       </c>
@@ -7734,7 +7730,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>588</v>
       </c>
@@ -7742,7 +7738,7 @@
         <v>51.51</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>589</v>
       </c>
@@ -7750,7 +7746,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>590</v>
       </c>
@@ -7758,7 +7754,7 @@
         <v>52.36</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>591</v>
       </c>
@@ -7766,7 +7762,7 @@
         <v>52.33</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>592</v>
       </c>
@@ -7774,7 +7770,7 @@
         <v>52.26</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>593</v>
       </c>
@@ -7782,7 +7778,7 @@
         <v>52.42</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>594</v>
       </c>
@@ -7790,7 +7786,7 @@
         <v>52.53</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>595</v>
       </c>
@@ -7798,7 +7794,7 @@
         <v>52.56</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>596</v>
       </c>
@@ -7806,7 +7802,7 @@
         <v>52.75</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>597</v>
       </c>
@@ -7814,7 +7810,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>598</v>
       </c>
@@ -7822,7 +7818,7 @@
         <v>53.54</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>599</v>
       </c>
@@ -7830,7 +7826,7 @@
         <v>54.18</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>600</v>
       </c>
@@ -7838,7 +7834,7 @@
         <v>54.71</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>601</v>
       </c>
@@ -7846,7 +7842,7 @@
         <v>54.96</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>602</v>
       </c>
@@ -7854,7 +7850,7 @@
         <v>55.17</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>603</v>
       </c>
@@ -7862,7 +7858,7 @@
         <v>55.51</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>604</v>
       </c>
@@ -7870,7 +7866,7 @@
         <v>55.49</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>605</v>
       </c>
@@ -7878,7 +7874,7 @@
         <v>55.51</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>606</v>
       </c>
@@ -7886,7 +7882,7 @@
         <v>55.67</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>607</v>
       </c>
@@ -7894,7 +7890,7 @@
         <v>55.66</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>608</v>
       </c>
@@ -7902,7 +7898,7 @@
         <v>55.82</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>609</v>
       </c>
@@ -7910,7 +7906,7 @@
         <v>55.99</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>610</v>
       </c>
@@ -7922,7 +7918,7 @@
         <v>4.0333552905956713</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>611</v>
       </c>
@@ -7934,7 +7930,7 @@
         <v>4.0434020834845263</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>612</v>
       </c>
@@ -7946,7 +7942,7 @@
         <v>4.0510890535511432</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>613</v>
       </c>
@@ -7958,7 +7954,7 @@
         <v>4.0556037339056701</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>614</v>
       </c>
@@ -7970,7 +7966,7 @@
         <v>4.0595805697857612</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>615</v>
       </c>
@@ -7982,7 +7978,7 @@
         <v>4.0635416530670554</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>616</v>
       </c>
@@ -7994,7 +7990,7 @@
         <v>4.0640571612836442</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>617</v>
       </c>
@@ -8006,7 +8002,7 @@
         <v>4.0640571612836442</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>618</v>
       </c>
@@ -8018,7 +8014,7 @@
         <v>4.0683427596830999</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>619</v>
       </c>
@@ -8030,7 +8026,7 @@
         <v>4.0707346965829672</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>620</v>
       </c>
@@ -8042,7 +8038,7 @@
         <v>4.0717580635493054</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>621</v>
       </c>
@@ -8054,7 +8050,7 @@
         <v>4.0724397268340509</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>622</v>
       </c>
@@ -8066,7 +8062,7 @@
         <v>4.0778763695147937</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>623</v>
       </c>
@@ -8078,7 +8074,7 @@
         <v>4.0844625623676496</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>624</v>
       </c>
@@ -8090,7 +8086,7 @@
         <v>4.0915072074019401</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>625</v>
       </c>
@@ -8102,7 +8098,7 @@
         <v>4.0958434383458364</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>626</v>
       </c>
@@ -8114,7 +8110,7 @@
         <v>4.0991662525013144</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>627</v>
       </c>
@@ -8126,7 +8122,7 @@
         <v>4.1023127318712778</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>628</v>
       </c>
@@ -8138,7 +8134,7 @@
         <v>4.106437809909484</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>629</v>
       </c>
@@ -8150,7 +8146,7 @@
         <v>4.110217911378391</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>630</v>
       </c>
@@ -8162,7 +8158,7 @@
         <v>4.1131663164626886</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>631</v>
       </c>
@@ -8174,7 +8170,7 @@
         <v>4.1116932005567133</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>632</v>
       </c>
@@ -8186,7 +8182,7 @@
         <v>4.1139837774744494</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>633</v>
       </c>
@@ -8198,7 +8194,7 @@
         <v>4.1162691196378924</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>634</v>
       </c>
@@ -8210,7 +8206,7 @@
         <v>4.1239033644636454</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>635</v>
       </c>
@@ -8222,7 +8218,7 @@
         <v>4.1356464415792065</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>636</v>
       </c>
@@ -8234,7 +8230,7 @@
         <v>4.147727338787214</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>637</v>
       </c>
@@ -8246,7 +8242,7 @@
         <v>4.1565365824785481</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>638</v>
       </c>
@@ -8258,7 +8254,7 @@
         <v>4.1596640283427435</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>639</v>
       </c>
@@ -8270,7 +8266,7 @@
         <v>4.1607563277413524</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>640</v>
       </c>
@@ -8282,7 +8278,7 @@
         <v>4.162470391269701</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>641</v>
       </c>
@@ -8294,7 +8290,7 @@
         <v>4.1610681942650087</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>642</v>
       </c>
@@ -8306,7 +8302,7 @@
         <v>4.1620032106959153</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>643</v>
       </c>
@@ -8318,7 +8314,7 @@
         <v>4.1620032106959153</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>644</v>
       </c>
@@ -8330,7 +8326,7 @@
         <v>4.1668202505441503</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>645</v>
       </c>
@@ -8342,7 +8338,7 @@
         <v>4.1716141977134011</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>646</v>
       </c>
@@ -8354,7 +8350,7 @@
         <v>4.1822028027437854</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>647</v>
       </c>
@@ -8366,7 +8362,7 @@
         <v>4.1972019476618083</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>648</v>
       </c>
@@ -8378,7 +8374,7 @@
         <v>4.2052894561738281</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>649</v>
       </c>
@@ -8390,7 +8386,7 @@
         <v>4.2122757350537796</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>650</v>
       </c>
@@ -8402,7 +8398,7 @@
         <v>4.2215644122328202</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>651</v>
       </c>
@@ -8414,7 +8410,7 @@
         <v>4.2301857851335143</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>652</v>
       </c>
@@ -8426,7 +8422,7 @@
         <v>4.2349756919618464</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>653</v>
       </c>
@@ -8438,7 +8434,7 @@
         <v>4.2368563435107198</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>654</v>
       </c>
@@ -8450,7 +8446,7 @@
         <v>4.2349756919618464</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>655</v>
       </c>
@@ -8462,7 +8458,7 @@
         <v>4.2384449061958573</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>656</v>
       </c>
@@ -8474,7 +8470,7 @@
         <v>4.241182857326236</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>657</v>
       </c>
@@ -8486,7 +8482,7 @@
         <v>4.2456340097683265</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>658</v>
       </c>
@@ -8498,7 +8494,7 @@
         <v>4.2514907510291575</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>659</v>
       </c>
@@ -8510,7 +8506,7 @@
         <v>4.2598590006996737</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>660</v>
       </c>
@@ -8522,7 +8518,7 @@
         <v>4.2647903245358618</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>661</v>
       </c>
@@ -8534,7 +8530,7 @@
         <v>4.2680177180620138</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>662</v>
       </c>
@@ -8546,7 +8542,7 @@
         <v>4.2681578035143692</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>663</v>
       </c>
@@ -8558,7 +8554,7 @@
         <v>4.2675973439228452</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>664</v>
       </c>
@@ -8570,7 +8566,7 @@
         <v>4.2671767929949391</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>665</v>
       </c>
@@ -8582,7 +8578,7 @@
         <v>4.2675973439228452</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>666</v>
       </c>
@@ -8594,7 +8590,7 @@
         <v>4.2666157831625542</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>667</v>
       </c>
@@ -8606,7 +8602,7 @@
         <v>4.2653523591157816</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>668</v>
       </c>
@@ -8618,7 +8614,7 @@
         <v>4.2646497665203089</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>669</v>
       </c>
@@ -8630,7 +8626,7 @@
         <v>4.2654928184179299</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>670</v>
       </c>
@@ -8642,7 +8638,7 @@
         <v>4.2723512678647806</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>671</v>
       </c>
@@ -8654,7 +8650,7 @@
         <v>4.2805474657240277</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>672</v>
       </c>
@@ -8666,7 +8662,7 @@
         <v>4.283034685466931</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>673</v>
       </c>
@@ -8678,7 +8674,7 @@
         <v>4.2875785831301663</v>
       </c>
     </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>674</v>
       </c>
@@ -8690,7 +8686,7 @@
         <v>4.2886770316821909</v>
       </c>
     </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>675</v>
       </c>
@@ -8702,7 +8698,7 @@
         <v>4.2897742749687948</v>
       </c>
     </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>676</v>
       </c>
@@ -8714,7 +8710,7 @@
         <v>4.289362949810462</v>
       </c>
     </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>677</v>
       </c>
@@ -8726,7 +8722,7 @@
         <v>4.290459441148391</v>
       </c>
     </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>678</v>
       </c>
@@ -8738,7 +8734,7 @@
         <v>4.2890886390146123</v>
       </c>
     </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>679</v>
       </c>
@@ -8750,7 +8746,7 @@
         <v>4.2882652548594073</v>
       </c>
     </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>680</v>
       </c>
@@ -8762,7 +8758,7 @@
         <v>4.2901854310083021</v>
       </c>
     </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>681</v>
       </c>
@@ -8774,7 +8770,7 @@
         <v>4.2966049026198867</v>
       </c>
     </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>682</v>
       </c>
@@ -8786,7 +8782,7 @@
         <v>4.3056854014171595</v>
       </c>
     </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>683</v>
       </c>
@@ -8798,7 +8794,7 @@
         <v>4.3117382815557033</v>
       </c>
     </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>684</v>
       </c>
@@ -8810,7 +8806,7 @@
         <v>4.3144167350118243</v>
       </c>
     </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>685</v>
       </c>
@@ -8822,7 +8818,7 @@
         <v>4.3156197024762832</v>
       </c>
     </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>686</v>
       </c>
@@ -8834,7 +8830,7 @@
         <v>4.3184210115849107</v>
       </c>
     </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>687</v>
       </c>
@@ -8846,7 +8842,7 @@
         <v>4.32161292811326</v>
       </c>
     </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>688</v>
       </c>
@@ -8858,7 +8854,7 @@
         <v>4.323072491830211</v>
       </c>
     </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>689</v>
       </c>
@@ -8870,7 +8866,7 @@
         <v>4.3226746402236103</v>
       </c>
     </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>690</v>
       </c>
@@ -8882,7 +8878,7 @@
         <v>4.325720798462787</v>
       </c>
     </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>691</v>
       </c>
@@ -8894,7 +8890,7 @@
         <v>4.3277024359432819</v>
       </c>
     </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>692</v>
       </c>
@@ -8906,7 +8902,7 @@
         <v>4.3290213493499836</v>
       </c>
     </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>693</v>
       </c>
@@ -8918,7 +8914,7 @@
         <v>4.3332302204849187</v>
       </c>
     </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>694</v>
       </c>
@@ -8930,7 +8926,7 @@
         <v>4.3405533864673069</v>
       </c>
     </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>695</v>
       </c>
@@ -8942,7 +8938,7 @@
         <v>4.3466584908360906</v>
       </c>
     </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>696</v>
       </c>
@@ -8954,7 +8950,7 @@
         <v>4.3478233133323831</v>
       </c>
     </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>697</v>
       </c>
@@ -8966,7 +8962,7 @@
         <v>4.349245145149502</v>
       </c>
     </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>698</v>
       </c>
@@ -8978,7 +8974,7 @@
         <v>4.3523403243035208</v>
       </c>
     </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>699</v>
       </c>
@@ -8990,7 +8986,7 @@
         <v>4.3531126245092393</v>
       </c>
     </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>700</v>
       </c>
@@ -9002,7 +8998,7 @@
         <v>4.3528552573736015</v>
       </c>
     </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>701</v>
       </c>
@@ -9014,7 +9010,7 @@
         <v>4.3532412832421281</v>
       </c>
     </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>702</v>
       </c>
@@ -9026,7 +9022,7 @@
         <v>4.3561958746393596</v>
       </c>
     </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>703</v>
       </c>
@@ -9038,7 +9034,7 @@
         <v>4.3577339421048373</v>
       </c>
     </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>704</v>
       </c>
@@ -9050,7 +9046,7 @@
         <v>4.3564523835544513</v>
       </c>
     </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>705</v>
       </c>
@@ -9062,7 +9058,7 @@
         <v>4.357349646961441</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>706</v>
       </c>
@@ -9074,7 +9070,7 @@
         <v>4.3602921425278751</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>707</v>
       </c>
@@ -9086,7 +9082,7 @@
         <v>4.3647533060034247</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>708</v>
       </c>
@@ -9098,7 +9094,7 @@
         <v>4.3667860852575968</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>709</v>
       </c>
@@ -9110,7 +9106,7 @@
         <v>4.369321262176328</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>710</v>
       </c>
@@ -9122,7 +9118,7 @@
         <v>4.3721025534761884</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>711</v>
       </c>
@@ -9134,7 +9130,7 @@
         <v>4.3743724157370218</v>
       </c>
     </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>712</v>
       </c>
@@ -9146,7 +9142,7 @@
         <v>4.374876130645041</v>
       </c>
     </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>713</v>
       </c>
@@ -9158,7 +9154,7 @@
         <v>4.3757570216602861</v>
       </c>
     </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>714</v>
       </c>
@@ -9170,7 +9166,7 @@
         <v>4.3786459265144044</v>
       </c>
     </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>715</v>
       </c>
@@ -9182,7 +9178,7 @@
         <v>4.3760085623483187</v>
       </c>
     </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>716</v>
       </c>
@@ -9194,7 +9190,7 @@
         <v>4.3738684469724181</v>
       </c>
     </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>717</v>
       </c>
@@ -9206,7 +9202,7 @@
         <v>4.3765114539857715</v>
       </c>
     </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>718</v>
       </c>
@@ -9218,7 +9214,7 @@
         <v>4.381401439279963</v>
       </c>
     </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>719</v>
       </c>
@@ -9230,7 +9226,7 @@
         <v>4.3876358734383922</v>
       </c>
     </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>720</v>
       </c>
@@ -9242,7 +9238,7 @@
         <v>4.3916056094542046</v>
       </c>
     </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>721</v>
       </c>
@@ -9254,7 +9250,7 @@
         <v>4.3961760577783009</v>
       </c>
     </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>722</v>
       </c>
@@ -9266,7 +9262,7 @@
         <v>4.4009710506748192</v>
       </c>
     </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>723</v>
       </c>
@@ -9278,7 +9274,7 @@
         <v>4.4019518034811513</v>
       </c>
     </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>724</v>
       </c>
@@ -9290,7 +9286,7 @@
         <v>4.403421131528038</v>
       </c>
     </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>725</v>
       </c>
@@ -9302,7 +9298,7 @@
         <v>4.4054989908590239</v>
       </c>
     </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>726</v>
       </c>
@@ -9314,7 +9310,7 @@
         <v>4.4068411910483203</v>
       </c>
     </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>727</v>
       </c>
@@ -9326,7 +9322,7 @@
         <v>4.4084251085284123</v>
       </c>
     </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>728</v>
       </c>
@@ -9338,7 +9334,7 @@
         <v>4.4097633896454811</v>
       </c>
     </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>729</v>
       </c>
@@ -9350,7 +9346,7 @@
         <v>4.4124345908452645</v>
       </c>
     </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>730</v>
       </c>
@@ -9362,7 +9358,7 @@
         <v>4.4188406077965983</v>
       </c>
     </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>731</v>
       </c>
@@ -9374,7 +9370,7 @@
         <v>4.4303404949524321</v>
       </c>
     </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>732</v>
       </c>
@@ -9386,7 +9382,7 @@
         <v>4.4361596432538093</v>
       </c>
     </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>733</v>
       </c>
@@ -9398,7 +9394,7 @@
         <v>4.4414740933173018</v>
       </c>
     </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>734</v>
       </c>
@@ -9410,7 +9406,7 @@
         <v>4.4440620255933343</v>
       </c>
     </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>735</v>
       </c>
@@ -9422,7 +9418,7 @@
         <v>4.4451187978398643</v>
       </c>
     </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>736</v>
       </c>
@@ -9434,7 +9430,7 @@
         <v>4.4469947510222152</v>
       </c>
     </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>737</v>
       </c>
@@ -9446,7 +9442,7 @@
         <v>4.4517858790887344</v>
       </c>
     </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>738</v>
       </c>
@@ -9458,7 +9454,7 @@
         <v>4.4588719283707929</v>
       </c>
     </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>739</v>
       </c>
@@ -9470,7 +9466,7 @@
         <v>4.4656782071694927</v>
       </c>
     </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>740</v>
       </c>
@@ -9482,7 +9478,7 @@
         <v>4.4717530725477399</v>
       </c>
     </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>741</v>
       </c>
@@ -9494,7 +9490,7 @@
         <v>4.4779048349422155</v>
       </c>
     </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>742</v>
       </c>
@@ -9506,7 +9502,7 @@
         <v>4.4907689256781156</v>
       </c>
     </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>743</v>
       </c>
@@ -9518,7 +9514,7 @@
         <v>4.5034696311617521</v>
       </c>
     </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>744</v>
       </c>
@@ -9530,7 +9526,7 @@
         <v>4.5128355747852957</v>
       </c>
     </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>745</v>
       </c>
@@ -9542,7 +9538,7 @@
         <v>4.5177587289771219</v>
       </c>
     </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>746</v>
       </c>
@@ -9554,7 +9550,7 @@
         <v>4.5228749432612609</v>
       </c>
     </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>747</v>
       </c>
@@ -9566,7 +9562,7 @@
         <v>4.5276409834788538</v>
       </c>
     </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>748</v>
       </c>
@@ -9578,7 +9574,7 @@
         <v>4.5328145237959507</v>
       </c>
     </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>749</v>
       </c>
@@ -9590,7 +9586,7 @@
         <v>4.5296920448121343</v>
       </c>
     </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>750</v>
       </c>
@@ -9602,7 +9598,7 @@
         <v>4.5291526995641753</v>
       </c>
     </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>751</v>
       </c>
@@ -9614,7 +9610,7 @@
         <v>4.5285051010526063</v>
       </c>
     </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>752</v>
       </c>
@@ -9626,7 +9622,7 @@
         <v>4.5296920448121343</v>
       </c>
     </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>753</v>
       </c>
@@ -9638,7 +9634,7 @@
         <v>4.5337815899004381</v>
       </c>
     </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>754</v>
       </c>
@@ -9650,7 +9646,7 @@
         <v>4.54403918598386</v>
       </c>
     </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>755</v>
       </c>
@@ -9662,7 +9658,7 @@
         <v>4.5539821492186583</v>
       </c>
     </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>756</v>
       </c>
@@ -9674,7 +9670,7 @@
         <v>4.5587073115777503</v>
       </c>
     </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>757</v>
       </c>
@@ -9686,7 +9682,7 @@
         <v>4.5634102517398594</v>
       </c>
     </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>758</v>
       </c>
@@ -9698,7 +9694,7 @@
         <v>4.5655974108682686</v>
       </c>
     </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>759</v>
       </c>
@@ -9710,7 +9706,7 @@
         <v>4.5667411593683092</v>
       </c>
     </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>760</v>
       </c>
@@ -9722,7 +9718,7 @@
         <v>4.566221435849517</v>
       </c>
     </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>761</v>
       </c>
@@ -9734,7 +9730,7 @@
         <v>4.5676759815605106</v>
       </c>
     </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>762</v>
       </c>
@@ -9746,7 +9742,7 @@
         <v>4.5680911777466706</v>
       </c>
     </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>763</v>
       </c>
@@ -9758,7 +9754,7 @@
         <v>4.5681949498631962</v>
       </c>
     </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>764</v>
       </c>
@@ -9770,7 +9766,7 @@
         <v>4.5700610088745233</v>
       </c>
     </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>765</v>
       </c>
@@ -9782,7 +9778,7 @@
         <v>4.5738858959483251</v>
       </c>
     </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>766</v>
       </c>
@@ -9794,7 +9790,7 @@
         <v>4.5801600229839234</v>
       </c>
     </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>767</v>
       </c>
@@ -9806,7 +9802,7 @@
         <v>4.5872098606110985</v>
       </c>
     </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>768</v>
       </c>
@@ -9818,7 +9814,7 @@
         <v>4.5895488050851343</v>
       </c>
     </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>769</v>
       </c>
@@ -9830,7 +9826,7 @@
         <v>4.5942103457517494</v>
       </c>
     </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>770</v>
       </c>
@@ -9842,7 +9838,7 @@
         <v>4.5967347071669895</v>
       </c>
     </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>771</v>
       </c>
@@ -9854,7 +9850,7 @@
         <v>4.5982462709152676</v>
       </c>
     </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>772</v>
       </c>
@@ -9866,7 +9862,7 @@
         <v>4.5969363810609876</v>
       </c>
     </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>773</v>
       </c>
@@ -9878,7 +9874,7 @@
         <v>4.598145571051127</v>
       </c>
     </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>774</v>
       </c>
@@ -9890,7 +9886,7 @@
         <v>4.5998560911643223</v>
       </c>
     </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>775</v>
       </c>
@@ -9902,7 +9898,7 @@
         <v>4.6010617579435484</v>
       </c>
     </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>776</v>
       </c>
@@ -9914,7 +9910,7 @@
         <v>4.6021656769677923</v>
       </c>
     </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>777</v>
       </c>
@@ -9926,7 +9922,7 @@
         <v>4.6051701859880918</v>
       </c>
     </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>778</v>
       </c>
@@ -9938,7 +9934,7 @@
         <v>4.6111522576656387</v>
       </c>
     </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>779</v>
       </c>
@@ -9950,7 +9946,7 @@
         <v>4.6169011088637903</v>
       </c>
     </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>780</v>
       </c>
@@ -9962,7 +9958,7 @@
         <v>4.6212403661655861</v>
       </c>
     </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>781</v>
       </c>
@@ -9974,7 +9970,7 @@
         <v>4.6261485923732835</v>
       </c>
     </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>782</v>
       </c>
@@ -9986,7 +9982,7 @@
         <v>4.6292772613313247</v>
       </c>
     </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>783</v>
       </c>
@@ -9998,7 +9994,7 @@
         <v>4.6319094831777132</v>
       </c>
     </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>784</v>
       </c>
@@ -10010,7 +10006,7 @@
         <v>4.6341462942246086</v>
       </c>
     </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>785</v>
       </c>
@@ -10022,7 +10018,7 @@
         <v>4.6350202079569769</v>
       </c>
     </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>786</v>
       </c>
@@ -10034,7 +10030,7 @@
         <v>4.637250079451503</v>
       </c>
     </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>787</v>
       </c>
@@ -10046,7 +10042,7 @@
         <v>4.6388950553897121</v>
       </c>
     </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>788</v>
       </c>
@@ -10058,7 +10054,7 @@
         <v>4.6399580114737553</v>
       </c>
     </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>789</v>
       </c>
@@ -10070,7 +10066,7 @@
         <v>4.6424659707317879</v>
       </c>
     </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>790</v>
       </c>
@@ -10082,7 +10078,7 @@
         <v>4.6466959328165895</v>
       </c>
     </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>791</v>
       </c>
@@ -10094,7 +10090,7 @@
         <v>4.6533887582585658</v>
       </c>
     </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>792</v>
       </c>
@@ -10106,7 +10102,7 @@
         <v>4.6589952726829988</v>
       </c>
     </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>793</v>
       </c>
@@ -10118,7 +10114,7 @@
         <v>4.6606048928761918</v>
       </c>
     </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>794</v>
       </c>
@@ -10130,7 +10126,7 @@
         <v>4.6573830574350259</v>
       </c>
     </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>795</v>
       </c>
@@ -10142,7 +10138,7 @@
         <v>4.6536745950477068</v>
       </c>
     </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>796</v>
       </c>
@@ -10154,7 +10150,7 @@
         <v>4.6536745950477068</v>
       </c>
     </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>797</v>
       </c>
@@ -10166,7 +10162,7 @@
         <v>4.6535793251957784</v>
       </c>
     </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>798</v>
       </c>
@@ -10178,7 +10174,7 @@
         <v>4.6567184478686681</v>
       </c>
     </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>799</v>
       </c>
@@ -10190,7 +10186,7 @@
         <v>4.6561484307527206</v>
       </c>
     </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>800</v>
       </c>
@@ -10202,7 +10198,7 @@
         <v>4.6547219648173392</v>
       </c>
     </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>801</v>
       </c>
@@ -10214,7 +10210,7 @@
         <v>4.6585213614850858</v>
       </c>
     </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>802</v>
       </c>
@@ -10226,7 +10222,7 @@
         <v>4.6625896768555775</v>
       </c>
     </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>803</v>
       </c>
@@ -10238,7 +10234,7 @@
         <v>4.6688958768686364</v>
       </c>
     </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>804</v>
       </c>
@@ -10250,7 +10246,7 @@
         <v>4.6739497013829174</v>
       </c>
     </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>805</v>
       </c>
@@ -10262,7 +10258,7 @@
         <v>4.6799065321021089</v>
       </c>
     </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>806</v>
       </c>
@@ -10274,7 +10270,7 @@
         <v>4.6898789139150452</v>
       </c>
     </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>807</v>
       </c>
@@ -10286,7 +10282,7 @@
         <v>4.6893274939948144</v>
       </c>
     </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>808</v>
       </c>
@@ -10298,7 +10294,7 @@
         <v>4.6926314617580855</v>
       </c>
     </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>809</v>
       </c>
@@ -10310,7 +10306,7 @@
         <v>4.6970198396179708</v>
       </c>
     </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>810</v>
       </c>
@@ -10322,7 +10318,7 @@
         <v>4.7008439360563736</v>
       </c>
     </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>811</v>
       </c>
@@ -10334,7 +10330,7 @@
         <v>4.701025671631613</v>
       </c>
     </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>812</v>
       </c>
@@ -10346,7 +10342,7 @@
         <v>4.7059200890882344</v>
       </c>
     </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>813</v>
       </c>
@@ -10358,7 +10354,7 @@
         <v>4.7132170900712254</v>
       </c>
     </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>814</v>
       </c>
@@ -10370,7 +10366,7 @@
         <v>4.7296860606856592</v>
       </c>
     </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>815</v>
       </c>
@@ -10382,7 +10378,7 @@
         <v>4.7458881929269703</v>
       </c>
     </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>816</v>
       </c>
@@ -10394,7 +10390,7 @@
         <v>4.7558290622732047</v>
       </c>
     </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>817</v>
       </c>
@@ -10406,7 +10402,7 @@
         <v>4.7682239724243889</v>
       </c>
     </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>818</v>
       </c>
@@ -10418,7 +10414,7 @@
         <v>4.7765993016156223</v>
       </c>
     </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>819</v>
       </c>
@@ -10430,7 +10426,7 @@
         <v>4.781725147887709</v>
       </c>
     </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>820</v>
       </c>
@@ -10442,7 +10438,7 @@
         <v>4.7897392153225251</v>
       </c>
     </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>821</v>
       </c>
@@ -10454,7 +10450,7 @@
         <v>4.7999142627806028</v>
       </c>
     </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>822</v>
       </c>
@@ -10466,7 +10462,7 @@
         <v>4.8091716917739342</v>
       </c>
     </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>823</v>
       </c>
@@ -10478,7 +10474,7 @@
         <v>4.8163221244499228</v>
       </c>
     </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>824</v>
       </c>
@@ -10490,7 +10486,7 @@
         <v>4.8239843791410717</v>
       </c>
     </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>825</v>
       </c>
@@ -10502,7 +10498,7 @@
         <v>4.8365199738494002</v>
       </c>
     </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>826</v>
       </c>
@@ -10514,7 +10510,7 @@
         <v>4.8541374173117591</v>
       </c>
     </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>827</v>
       </c>
@@ -10526,7 +10522,7 @@
         <v>4.8706066494925526</v>
       </c>
     </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>828</v>
       </c>
@@ -10538,7 +10534,7 @@
         <v>4.8810579785571608</v>
       </c>
     </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>829</v>
       </c>
@@ -10550,7 +10546,7 @@
         <v>4.888844237042334</v>
       </c>
     </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>830</v>
       </c>
@@ -10562,7 +10558,7 @@
         <v>4.8932021972041602</v>
       </c>
     </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>831</v>
       </c>
@@ -10574,7 +10570,7 @@
         <v>4.8961966596902622</v>
       </c>
     </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>832</v>
       </c>
@@ -10586,7 +10582,7 @@
         <v>4.901192382714874</v>
       </c>
     </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>833</v>
       </c>
@@ -10598,7 +10594,7 @@
         <v>4.9081595025070195</v>
       </c>
     </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>834</v>
       </c>
@@ -10610,7 +10606,7 @@
         <v>4.9134633823439824</v>
       </c>
     </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>835</v>
       </c>
@@ -10622,7 +10618,7 @@
         <v>4.9159582471543475</v>
       </c>
     </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>836</v>
       </c>
@@ -10634,7 +10630,7 @@
         <v>4.920637644447809</v>
       </c>
     </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>837</v>
       </c>
@@ -10646,7 +10642,7 @@
         <v>4.9252226384703226</v>
       </c>
     </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>838</v>
       </c>
@@ -10658,7 +10654,7 @@
         <v>4.9343300378861814</v>
       </c>
     </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>839</v>
       </c>
@@ -10670,7 +10666,7 @@
         <v>4.9451363118635605</v>
       </c>
     </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>840</v>
       </c>
@@ -10682,7 +10678,7 @@
         <v>4.9521583643372802</v>
       </c>
     </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>841</v>
       </c>
@@ -10694,7 +10690,7 @@
         <v>4.9580780433575793</v>
       </c>
     </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>842</v>
       </c>
@@ -10706,7 +10702,7 @@
         <v>4.9622850331552089</v>
       </c>
     </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>843</v>
       </c>
@@ -10718,7 +10714,7 @@
         <v>4.965498448424726</v>
       </c>
     </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>844</v>
       </c>
@@ -10730,7 +10726,7 @@
         <v>4.9675190030226277</v>
       </c>
     </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>845</v>
       </c>
@@ -10742,7 +10738,7 @@
         <v>4.9675190030226277</v>
       </c>
     </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>846</v>
       </c>
@@ -10754,7 +10750,7 @@
         <v>4.969952178820721</v>
       </c>
     </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>847</v>
       </c>
@@ -10766,7 +10762,7 @@
         <v>4.9686320466157978</v>
       </c>
     </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>848</v>
       </c>
@@ -10778,7 +10774,7 @@
         <v>4.9713399114886139</v>
       </c>
     </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>849</v>
       </c>
@@ -10790,7 +10786,7 @@
         <v>4.9759058135751575</v>
       </c>
     </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>850</v>
       </c>
@@ -10802,7 +10798,7 @@
         <v>4.9852491077058403</v>
       </c>
     </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>851</v>
       </c>
@@ -10814,7 +10810,7 @@
         <v>4.996536369716754</v>
       </c>
     </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>852</v>
       </c>
@@ -10826,7 +10822,7 @@
         <v>5.0017963454290513</v>
       </c>
     </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>853</v>
       </c>
@@ -10838,7 +10834,7 @@
         <v>5.0083660546522122</v>
       </c>
     </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>854</v>
       </c>
@@ -10850,7 +10846,7 @@
         <v>5.011568192144856</v>
       </c>
     </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>855</v>
       </c>
@@ -10862,7 +10858,7 @@
         <v>5.0126332967589287</v>
       </c>
     </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>856</v>
       </c>
@@ -10874,7 +10870,7 @@
         <v>5.0153574604315851</v>
       </c>
     </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>857</v>
       </c>
@@ -10886,7 +10882,7 @@
         <v>5.0172136094563786</v>
       </c>
     </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>858</v>
       </c>
@@ -10898,7 +10894,7 @@
         <v>5.0204536030335944</v>
       </c>
     </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>859</v>
       </c>
@@ -10910,7 +10906,7 @@
         <v>5.0223003256267589</v>
       </c>
     </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>860</v>
       </c>
@@ -10922,7 +10918,7 @@
         <v>5.0230248917421783</v>
       </c>
     </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>861</v>
       </c>
@@ -10934,7 +10930,7 @@
         <v>5.0256552608526412</v>
       </c>
     </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>862</v>
       </c>
@@ -10946,17 +10942,17 @@
         <v>5.0374070445936834</v>
       </c>
     </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>864</v>
       </c>
@@ -10970,7 +10966,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -10979,7 +10975,7 @@
     <col min="5" max="5" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>865</v>
       </c>
@@ -10996,7 +10992,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
